--- a/backtest_runs/20260410_193731/filter/BECO/BECO.xlsx
+++ b/backtest_runs/20260410_193731/filter/BECO/BECO.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-3076.919999999993</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>96923.08</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>96923.08</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>96923.08</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>96923.08</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>96923.08</v>
@@ -909,7 +909,7 @@
         <v>-2857.139999999998</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>94065.94</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>94945.06000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-3736.259999999998</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>93406.60000000002</v>
@@ -1231,7 +1231,7 @@
         <v>-1978.020000000016</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>91428.58</v>
@@ -1277,7 +1277,7 @@
         <v>-6593.399999999996</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>84835.18000000001</v>
@@ -1415,7 +1415,7 @@
         <v>-3516.480000000003</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>88351.66000000002</v>
@@ -1461,7 +1461,7 @@
         <v>-1318.679999999991</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>87032.98000000003</v>
@@ -1553,7 +1553,7 @@
         <v>-219.7800000000148</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>87692.32000000001</v>
@@ -1645,7 +1645,7 @@
         <v>-3296.699999999988</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>100879.12</v>
